--- a/QA_report/bug_report.xlsx
+++ b/QA_report/bug_report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>BUG ID</t>
   </si>
@@ -114,6 +114,15 @@
   </si>
   <si>
     <t>Suggestion: The Not started projects should be grayed out</t>
+  </si>
+  <si>
+    <t>3a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data is not persisting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Change the state of a Task and refeash </t>
   </si>
 </sst>
 </file>
@@ -434,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H8"/>
+  <dimension ref="A2:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
@@ -489,6 +498,9 @@
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -597,6 +609,26 @@
       </c>
       <c r="F8" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/QA_report/bug_report.xlsx
+++ b/QA_report/bug_report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>BUG ID</t>
   </si>
@@ -57,9 +57,6 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>The Complete button does not change to until you refresh the page</t>
-  </si>
-  <si>
     <t xml:space="preserve">User is on any Project </t>
   </si>
   <si>
@@ -68,9 +65,6 @@
   </si>
   <si>
     <t>Screenshot</t>
-  </si>
-  <si>
-    <t>When you complete all the Task in one project, the remaining Tasks in the other project comes completed too</t>
   </si>
   <si>
     <t>1. Complete all the Tasks in Website Redesign.
@@ -122,7 +116,16 @@
     <t xml:space="preserve">Data is not persisting </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Change the state of a Task and refeash </t>
+    <t>1. Change the state of a Task and refresh</t>
+  </si>
+  <si>
+    <t>The Complete button does not change until you refresh the page</t>
+  </si>
+  <si>
+    <t>When you complete all the Task in one project, the remaining Tasks in the other project becomes completed too</t>
+  </si>
+  <si>
+    <t>This is an issue relating to BUG 5</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -487,7 +490,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -496,10 +499,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -507,13 +510,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
@@ -527,13 +530,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
@@ -541,8 +544,11 @@
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -550,22 +556,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -573,13 +579,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
@@ -596,19 +602,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -616,19 +622,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/QA_report/bug_report.xlsx
+++ b/QA_report/bug_report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>BUG ID</t>
   </si>
@@ -64,14 +64,8 @@
 2. Check the state of the button</t>
   </si>
   <si>
-    <t>Screenshot</t>
-  </si>
-  <si>
     <t>1. Complete all the Tasks in Website Redesign.
 2. Check the other Projects</t>
-  </si>
-  <si>
-    <t>Critical</t>
   </si>
   <si>
     <t>User has to refresh before a Task is moved to the Reopen state when the user clicks on it</t>
@@ -126,6 +120,27 @@
   </si>
   <si>
     <t>This is an issue relating to BUG 5</t>
+  </si>
+  <si>
+    <t>SCREENSHOTS</t>
+  </si>
+  <si>
+    <t>Who is hurt</t>
+  </si>
+  <si>
+    <t>end user</t>
+  </si>
+  <si>
+    <t>data integrity</t>
+  </si>
+  <si>
+    <t>cosmetic</t>
+  </si>
+  <si>
+    <t>blocker</t>
+  </si>
+  <si>
+    <t>major</t>
   </si>
 </sst>
 </file>
@@ -446,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H9"/>
+  <dimension ref="A2:I9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
@@ -454,9 +469,10 @@
     <col min="4" max="4" width="21.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.88671875" customWidth="1"/>
     <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -479,10 +495,13 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -490,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -499,18 +518,21 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -522,119 +544,137 @@
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
